--- a/src/test/java/apachePOI/ScenarioResults.xlsx
+++ b/src/test/java/apachePOI/ScenarioResults.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="9">
   <si>
     <t>Login using credentials from Excel with Apache POI</t>
   </si>
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,248 @@
         <v>7</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
